--- a/Outputs/Scenarios/PtX_demand_SE_Hydrogen.xlsx
+++ b/Outputs/Scenarios/PtX_demand_SE_Hydrogen.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.004466517697420779</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01166627686077768</v>
+        <v>0.006475259306487512</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.003888758953592559</v>
+        <v>0.0090779748230327</v>
       </c>
     </row>
     <row r="18">
@@ -1481,7 +1481,7 @@
         <v>6.435495947338796e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.003888758953592559</v>
+        <v>0.003890560638442585</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.006612135668584872</v>
       </c>
       <c r="K30" t="n">
-        <v>0.06286494926617014</v>
+        <v>0.03489260992563983</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.02095498308872338</v>
+        <v>0.04891761386258395</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>0.0003480071404518354</v>
       </c>
       <c r="K42" t="n">
-        <v>0.02095498308872338</v>
+        <v>0.02096469165539312</v>
       </c>
     </row>
     <row r="43">
